--- a/public/system/export/borrowdetail.xlsx
+++ b/public/system/export/borrowdetail.xlsx
@@ -42,9 +42,6 @@
     <t>Ngày tạo:</t>
   </si>
   <si>
-    <t>Dạy môn:</t>
-  </si>
-  <si>
     <t>STT</t>
   </si>
   <si>
@@ -73,6 +70,9 @@
   </si>
   <si>
     <t>Độc lập - Tự do - Hạnh phúc</t>
+  </si>
+  <si>
+    <t>Tổ CM:</t>
   </si>
 </sst>
 </file>
@@ -433,7 +433,7 @@
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
@@ -465,7 +465,7 @@
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
@@ -642,8 +642,8 @@
       <c r="Z7" s="3"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>7</v>
+      <c r="A8" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="2"/>
@@ -701,28 +701,28 @@
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
       <c r="A10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
